--- a/check_in_forms/026_rv_service_check_in_form--check_in_forms.xlsx
+++ b/check_in_forms/026_rv_service_check_in_form--check_in_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>american_express</t>
+          <t>american express</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>oil_change</t>
+          <t>oil change</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tire_rotation</t>
+          <t>tire rotation</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>brake_pads</t>
+          <t>brake pads</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>battery_change</t>
+          <t>battery change</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>oil_filter</t>
+          <t>oil filter</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>spark_plugs</t>
+          <t>spark plugs</t>
         </is>
       </c>
     </row>
